--- a/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
+++ b/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Инженерно-техническая поддержка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Поддержка ИС охватывает пользователей, серверы, сеть, СУБД и данные. Студент разберёт, какие работы входят в поддержку, кто их выполняет и чем они отличаются от разработки.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инженерно-техническая поддержка</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">поддержка, инфраструктура, служба поддержки, зона ответственности, регламент</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «ITIL и процессы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">ITIL описывает поддержку как набор связанных процессов: инциденты, проблемы, изменения, запросы, релизы. Студент разберёт входы, выходы и владельцев каждого процесса.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITIL и процессы</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t xml:space="preserve">ITIL, процесс, владелец процесса, вход и выход, практика</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Регламент поддержки; SLA.</t>
+          <t xml:space="preserve">Студент пишет регламент поддержки учебной ИС: каналы приёма, категории, сроки, эскалация. Затем составляет SLA с уровнями сервиса и условиями пересмотра. Сдаёт оба документа.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регламент поддержки, SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">регламент, категория обращения, срок реакции, эскалация, уровень сервиса</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «SLA и SLO»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">SLA фиксирует обещание заказчику, SLO задаёт внутреннюю цель, SLI даёт измерение. Студент разберёт, как связаны три уровня и почему нельзя обещать больше, чем измеряешь.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA и SLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">SLA, SLO, SLI, показатель, отчётный период</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Инциденты»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Инцидент это любое событие, которое снижает качество услуги. Студент разберёт приоритеты, сроки реакции, маршрут эскалации и порядок закрытия обращения.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инциденты</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t xml:space="preserve">инцидент, влияние, срочность, приоритет, эскалация</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Инцидент; Проблема.</t>
+          <t xml:space="preserve">Студент обрабатывает серию инцидентов в учебной системе, находит общую причину и оформляет проблему. Сдаёт журнал инцидентов и карточку проблемы с планом устранения.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инцидент, Проблема</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">журнал инцидентов, общая причина, карточка проблемы, обходное решение, устранение причины</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проблемы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проблема это неизвестная причина одного или нескольких инцидентов. Студент разберёт поиск корневой причины, временное обходное решение и постоянное исправление.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проблемы</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">проблема, корневая причина, обходное решение, постоянное исправление, известная ошибка</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Запросы на обслуживание»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Запрос на обслуживание это штатная просьба пользователя: доступ, оборудование, консультация. Студент разберёт, чем запрос отличается от инцидента и как его выполнять по каталогу услуг.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запросы на обслуживание</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t xml:space="preserve">запрос на обслуживание, каталог услуг, согласование, исполнение, подтверждение</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Запрос; Мониторинг.</t>
+          <t xml:space="preserve">Студент выполняет запросы пользователей по каталогу услуг и настраивает мониторинг учебного сервера: датчики, пороги, оповещения. Сдаёт журнал запросов и карту мониторинга.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрос, Мониторинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t xml:space="preserve">каталог услуг, датчик, порог, оповещение, карта мониторинга</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
@@ -465,16 +465,16 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Мониторинг»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Мониторинг следит за доступностью, нагрузкой и ошибками системы. Студент разберёт виды датчиков, пороги срабатывания, оповещения и проблему ложных тревог.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t xml:space="preserve">датчик, метрика, порог, оповещение, ложная тревога</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Журналы»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент ищет причину сбоя по журналам учебного сервера и приложения: фильтрует записи по времени и уровню, сопоставляет события. Сдаёт выписку из журнала с разбором хронологии.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Журналы</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t xml:space="preserve">журнал, уровень записи, фильтр, хронология, источник события</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Журналы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Журналы системы, приложения и безопасности фиксируют события с разной детализацией. Студент разберёт уровни записей, ротацию файлов и требования к хранению.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Журналы</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t xml:space="preserve">системный журнал, прикладной журнал, уровень записи, ротация, срок хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Диагностика»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент диагностирует сбой учебного сервера по шагам: проверяет питание и доступность, сеть, диск, службы, приложение. Сдаёт карту диагностики с найденной причиной.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">диагностика, доступность, узкое место, проверка по шагам, карта диагностики</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диагностика»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Диагностика идёт от общего к частному: доступность узла, сеть, ресурсы, службы, приложение. Студент разберёт типовые симптомы и инструменты проверки на каждом шаге.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t xml:space="preserve">симптом, уровень проверки, диагностика, инструмент, гипотеза</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Серверы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Серверное железо и его ресурсы: процессор, память, диски, питание, охлаждение. Студент разберёт, как отказ каждого узла проявляется в работе ИС.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серверы</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t xml:space="preserve">процессор, оперативная память, дисковый массив, блок питания, охлаждение</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19-20</t>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сервер; Сеть.</t>
+          <t xml:space="preserve">Студент проверяет учебный сервер и сеть до него: ресурсы, службы, адресацию, маршрут, порты. Сдаёт протокол проверки с найденными отклонениями и мерами устранения.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сервер, Сеть</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t xml:space="preserve">ресурсы сервера, служба, адресация, маршрут, порт</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сеть»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сеть связывает пользователей с серверами ИС. Студент разберёт адресацию, маршрутизацию, порты и типовые причины потери связи с системой.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сеть</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t xml:space="preserve">IP-адрес, маршрут, порт, DNS, потеря пакетов</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «СУБД»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">СУБД отвечает за хранение и доступ к данным. Студент разберёт состояние экземпляра, блокировки, рост файлов и медленные запросы, которые чаще всего вызывают сбои.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">СУБД</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t xml:space="preserve">экземпляр, блокировка, журнал транзакций, медленный запрос, свободное место</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23-24</t>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: СУБД; Резервное копирование.</t>
+          <t xml:space="preserve">Студент проверяет состояние учебной СУБД, затем делает полную и разностную копию базы, проверяет её целостность и восстанавливает на тестовый экземпляр. Сдаёт скрипты и протокол.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">СУБД, Резервное копирование</t>
+          <t xml:space="preserve">полная копия, разностная копия, целостность, тестовый экземпляр, сверка данных</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Резервное копирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Резервная копия защищает от потери данных, но только если её проверяют. Студент разберёт схемы копирования, глубину хранения и правило трёх копий.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка копии</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Восстановление»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Восстановление возвращает систему к работе после сбоя. Студент разберёт точки восстановления, порядок действий, проверку целостности и фиксацию потерь данных.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t xml:space="preserve">точка восстановления, RTO, RPO, целостность, потеря данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Восстановление; Обновление.</t>
+          <t xml:space="preserve">Студент восстанавливает учебную базу из копии после смоделированного сбоя, затем устанавливает обновление на тестовый стенд и проверяет работу системы. Сдаёт протоколы восстановления и обновления.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление, Обновление</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t xml:space="preserve">восстановление, тестовый стенд, обновление, проверка после обновления, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Обновления»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Обновления закрывают уязвимости и добавляют функции, но могут сломать работу. Студент разберёт порядок установки, тестовый стенд, окно обслуживания и план отката.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обновления</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">обновление, исправление, тестовый стенд, окно обслуживания, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Безопасность»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу: пароли, права, журналы, обновления, резервные копии. Сдаёт заполненный чек-лист с перечнем слабых мест и планом устранения.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t xml:space="preserve">парольная политика, права, уязвимость, журнал доступа, план устранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
@@ -915,16 +915,16 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Безопасность поддержки: разграничение доступа, защита каналов, журналирование действий и защита резервных копий. Студент разберёт типовые ошибки администрирования.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование, защита копий</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
@@ -945,16 +945,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Доступы»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент оформляет и выполняет заявки на доступ: создаёт учётные записи, назначает роли, ограничивает права, блокирует уволенных. Сдаёт журнал доступов и матрицу ролей.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доступы</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t xml:space="preserve">учётная запись, роль, матрица прав, блокировка, заявка на доступ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Доступы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Управление доступами: учётные записи, роли, группы, права на объекты и регулярная проверка. Студент разберёт, как накапливаются лишние права и чем это опасно.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доступы</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t xml:space="preserve">учётная запись, роль, группа, проверка прав, отзыв доступа</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «База знаний»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент пополняет базу знаний по учебной ИС: пишет статью по типовому обращению, прикладывает решение и проверяет её на коллеге. Сдаёт три статьи и результат проверки.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">База знаний</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">статья, симптом, причина, решение, проверка статьи</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1035,16 +1035,16 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Документация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Документация поддержки: регламенты, инструкции, схемы инфраструктуры, журналы и отчёты. Студент разберёт, кто читает каждый документ и как поддерживать его в актуальном виде.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t xml:space="preserve">регламент, инструкция, схема инфраструктуры, версия, актуализация</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Метрики»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент собирает метрики поддержки за период: число обращений, время реакции, время решения, доля выполненных SLA. Сдаёт сводную таблицу и графики с выводами.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t xml:space="preserve">число обращений, время реакции, время решения, сводка, график</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
@@ -1095,16 +1095,16 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «База знаний»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">База знаний снижает нагрузку на поддержку и ускоряет решение. Студент разберёт структуру статей, поиск, проверку актуальности и связь статей с обращениями.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">База знаний</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t xml:space="preserve">статья, категория, поиск, актуальность, типовое обращение</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">38</t>
@@ -1125,16 +1125,16 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Отчёт»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент готовит отчёт о работе поддержки за месяц: объём обращений, соблюдение SLA, повторные обращения, узкие места. Сдаёт отчёт с таблицами и предложениями.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t xml:space="preserve">отчётный период, соблюдение SLA, повторное обращение, узкое место, предложение</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
@@ -1155,16 +1155,16 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Коммуникации»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Поддержка это разговор с человеком в стрессе. Студент разберёт структуру обращения, уточняющие вопросы, информирование о ходе работ и работу с недовольным пользователем.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Коммуникации</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t xml:space="preserve">уточняющий вопрос, структура обращения, информирование, конфликт, обратная связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
@@ -1185,16 +1185,16 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговый кейс»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент проходит полный цикл поддержки на учебном кейсе: приём обращения, диагностика, решение, запись в базу знаний, отчёт. Сдаёт пакет документов по кейсу.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговый кейс</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t xml:space="preserve">кейс, приём обращения, диагностика, закрытие, пакет документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
@@ -1215,16 +1215,16 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Аутсорсинг»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Часть поддержки можно передать внешнему подрядчику. Студент разберёт, какие работы отдают на аутсорсинг, как описать услугу и что контролировать по договору.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аутсорсинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+          <t xml:space="preserve">аутсорсинг, подрядчик, договор, показатель услуги, контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
@@ -1245,16 +1245,16 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Метрики»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Метрики поддержки показывают нагрузку, скорость и качество. Студент разберёт, какие показатели считать, как их не подделать и почему среднее время скрывает проблемы.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t xml:space="preserve">время реакции, время решения, повторное обращение, среднее и медиана, загрузка</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43</t>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Отчётность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Отчётность перед руководством и заказчиком: периодичность, состав показателей, выводы и предложения. Студент разберёт, как из журналов получается отчёт с решениями.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчётность</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
+          <t xml:space="preserve">структура отчёта, периодичность, показатель, вывод, предложение</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Непрерывность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Непрерывность бизнеса: что делать, если система недоступна. Студент разберёт план аварийного восстановления, резервные площадки и допустимое время простоя.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Непрерывность</t>
+          <t xml:space="preserve">непрерывность, аварийное восстановление, резервная площадка, время простоя, учебный запуск</t>
         </is>
       </c>
     </row>

--- a/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
+++ b/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>3960</v>
+        <v>88</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>

--- a/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
+++ b/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
@@ -237,60 +237,60 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Регламент поддержки; SLA</t>
+          <t xml:space="preserve">Лекция 3. SLA и SLO</t>
         </is>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пишет регламент поддержки учебной ИС: каналы приёма, категории, сроки, эскалация. Затем составляет SLA с уровнями сервиса и условиями пересмотра. Сдаёт оба документа.</t>
+          <t xml:space="preserve">SLA фиксирует обещание заказчику, SLO задаёт внутреннюю цель, SLI даёт измерение. Студент разберёт, как связаны три уровня и почему нельзя обещать больше, чем измеряешь.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">регламент, категория обращения, срок реакции, эскалация, уровень сервиса</t>
+          <t xml:space="preserve">SLA, SLO, SLI, показатель, отчётный период</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4-5</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. SLA и SLO</t>
+          <t xml:space="preserve">Практика 1. Регламент поддержки; SLA</t>
         </is>
       </c>
       <c r="D9" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA фиксирует обещание заказчику, SLO задаёт внутреннюю цель, SLI даёт измерение. Студент разберёт, как связаны три уровня и почему нельзя обещать больше, чем измеряешь.</t>
+          <t xml:space="preserve">Студент пишет регламент поддержки учебной ИС: каналы приёма, категории, сроки, эскалация. Затем составляет SLA с уровнями сервиса и условиями пересмотра. Сдаёт оба документа.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA, SLO, SLI, показатель, отчётный период</t>
+          <t xml:space="preserve">регламент, категория обращения, срок реакции, эскалация, уровень сервиса</t>
         </is>
       </c>
     </row>
@@ -327,60 +327,60 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Инцидент; Проблема</t>
+          <t xml:space="preserve">Лекция 5. Проблемы</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент обрабатывает серию инцидентов в учебной системе, находит общую причину и оформляет проблему. Сдаёт журнал инцидентов и карточку проблемы с планом устранения.</t>
+          <t xml:space="preserve">Проблема это неизвестная причина одного или нескольких инцидентов. Студент разберёт поиск корневой причины, временное обходное решение и постоянное исправление.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал инцидентов, общая причина, карточка проблемы, обходное решение, устранение причины</t>
+          <t xml:space="preserve">проблема, корневая причина, обходное решение, постоянное исправление, известная ошибка</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8-9</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Проблемы</t>
+          <t xml:space="preserve">Практика 2. Инцидент; Проблема</t>
         </is>
       </c>
       <c r="D12" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проблема это неизвестная причина одного или нескольких инцидентов. Студент разберёт поиск корневой причины, временное обходное решение и постоянное исправление.</t>
+          <t xml:space="preserve">Студент обрабатывает серию инцидентов в учебной системе, находит общую причину и оформляет проблему. Сдаёт журнал инцидентов и карточку проблемы с планом устранения.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">проблема, корневая причина, обходное решение, постоянное исправление, известная ошибка</t>
+          <t xml:space="preserve">журнал инцидентов, общая причина, карточка проблемы, обходное решение, устранение причины</t>
         </is>
       </c>
     </row>
@@ -417,60 +417,60 @@
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Запрос; Мониторинг</t>
+          <t xml:space="preserve">Лекция 7. Мониторинг</t>
         </is>
       </c>
       <c r="D14" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент выполняет запросы пользователей по каталогу услуг и настраивает мониторинг учебного сервера: датчики, пороги, оповещения. Сдаёт журнал запросов и карту мониторинга.</t>
+          <t xml:space="preserve">Мониторинг следит за доступностью, нагрузкой и ошибками системы. Студент разберёт виды датчиков, пороги срабатывания, оповещения и проблему ложных тревог.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">каталог услуг, датчик, порог, оповещение, карта мониторинга</t>
+          <t xml:space="preserve">датчик, метрика, порог, оповещение, ложная тревога</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12-13</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Мониторинг</t>
+          <t xml:space="preserve">Практика 3. Запрос; Мониторинг</t>
         </is>
       </c>
       <c r="D15" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг следит за доступностью, нагрузкой и ошибками системы. Студент разберёт виды датчиков, пороги срабатывания, оповещения и проблему ложных тревог.</t>
+          <t xml:space="preserve">Студент выполняет запросы пользователей по каталогу услуг и настраивает мониторинг учебного сервера: датчики, пороги, оповещения. Сдаёт журнал запросов и карту мониторинга.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">датчик, метрика, порог, оповещение, ложная тревога</t>
+          <t xml:space="preserve">каталог услуг, датчик, порог, оповещение, карта мониторинга</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Журналы</t>
+          <t xml:space="preserve">Лекция 8. Журналы</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент ищет причину сбоя по журналам учебного сервера и приложения: фильтрует записи по времени и уровню, сопоставляет события. Сдаёт выписку из журнала с разбором хронологии.</t>
+          <t xml:space="preserve">Журналы системы, приложения и безопасности фиксируют события с разной детализацией. Студент разберёт уровни записей, ротацию файлов и требования к хранению.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал, уровень записи, фильтр, хронология, источник события</t>
+          <t xml:space="preserve">системный журнал, прикладной журнал, уровень записи, ротация, срок хранения</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Журналы</t>
+          <t xml:space="preserve">Практика 4. Журналы</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Журналы системы, приложения и безопасности фиксируют события с разной детализацией. Студент разберёт уровни записей, ротацию файлов и требования к хранению.</t>
+          <t xml:space="preserve">Студент ищет причину сбоя по журналам учебного сервера и приложения: фильтрует записи по времени и уровню, сопоставляет события. Сдаёт выписку из журнала с разбором хронологии.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">системный журнал, прикладной журнал, уровень записи, ротация, срок хранения</t>
+          <t xml:space="preserve">журнал, уровень записи, фильтр, хронология, источник события</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Диагностика</t>
+          <t xml:space="preserve">Лекция 9. Диагностика</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент диагностирует сбой учебного сервера по шагам: проверяет питание и доступность, сеть, диск, службы, приложение. Сдаёт карту диагностики с найденной причиной.</t>
+          <t xml:space="preserve">Диагностика идёт от общего к частному: доступность узла, сеть, ресурсы, службы, приложение. Студент разберёт типовые симптомы и инструменты проверки на каждом шаге.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">диагностика, доступность, узкое место, проверка по шагам, карта диагностики</t>
+          <t xml:space="preserve">симптом, уровень проверки, диагностика, инструмент, гипотеза</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Диагностика</t>
+          <t xml:space="preserve">Практика 5. Диагностика</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика идёт от общего к частному: доступность узла, сеть, ресурсы, службы, приложение. Студент разберёт типовые симптомы и инструменты проверки на каждом шаге.</t>
+          <t xml:space="preserve">Студент диагностирует сбой учебного сервера по шагам: проверяет питание и доступность, сеть, диск, службы, приложение. Сдаёт карту диагностики с найденной причиной.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">симптом, уровень проверки, диагностика, инструмент, гипотеза</t>
+          <t xml:space="preserve">диагностика, доступность, узкое место, проверка по шагам, карта диагностики</t>
         </is>
       </c>
     </row>
@@ -624,63 +624,63 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 11. Сеть</t>
+        </is>
+      </c>
+      <c r="D21" s="6">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сеть связывает пользователей с серверами ИС. Студент разберёт адресацию, маршрутизацию, порты и типовые причины потери связи с системой.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IP-адрес, маршрут, порт, DNS, потеря пакетов</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20-21</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика 6. Сервер; Сеть</t>
         </is>
       </c>
-      <c r="D21" s="6">
+      <c r="D22" s="6">
         <v>4</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студент проверяет учебный сервер и сеть до него: ресурсы, службы, адресацию, маршрут, порты. Сдаёт протокол проверки с найденными отклонениями и мерами устранения.</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">ресурсы сервера, служба, адресация, маршрут, порт</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 11. Сеть</t>
-        </is>
-      </c>
-      <c r="D22" s="6">
-        <v>2</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сеть связывает пользователей с серверами ИС. Студент разберёт адресацию, маршрутизацию, порты и типовые причины потери связи с системой.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IP-адрес, маршрут, порт, DNS, потеря пакетов</t>
         </is>
       </c>
     </row>
@@ -714,63 +714,63 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 13. Резервное копирование</t>
+        </is>
+      </c>
+      <c r="D24" s="6">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Резервная копия защищает от потери данных, но только если её проверяют. Студент разберёт схемы копирования, глубину хранения и правило трёх копий.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка копии</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-25</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика 7. СУБД; Резервное копирование</t>
         </is>
       </c>
-      <c r="D24" s="6">
+      <c r="D25" s="6">
         <v>4</v>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студент проверяет состояние учебной СУБД, затем делает полную и разностную копию базы, проверяет её целостность и восстанавливает на тестовый экземпляр. Сдаёт скрипты и протокол.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">полная копия, разностная копия, целостность, тестовый экземпляр, сверка данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 13. Резервное копирование</t>
-        </is>
-      </c>
-      <c r="D25" s="6">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Резервная копия защищает от потери данных, но только если её проверяют. Студент разберёт схемы копирования, глубину хранения и правило трёх копий.</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка копии</t>
         </is>
       </c>
     </row>
@@ -807,60 +807,60 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Восстановление; Обновление</t>
+          <t xml:space="preserve">Лекция 15. Обновления</t>
         </is>
       </c>
       <c r="D27" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент восстанавливает учебную базу из копии после смоделированного сбоя, затем устанавливает обновление на тестовый стенд и проверяет работу системы. Сдаёт протоколы восстановления и обновления.</t>
+          <t xml:space="preserve">Обновления закрывают уязвимости и добавляют функции, но могут сломать работу. Студент разберёт порядок установки, тестовый стенд, окно обслуживания и план отката.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">восстановление, тестовый стенд, обновление, проверка после обновления, откат</t>
+          <t xml:space="preserve">обновление, исправление, тестовый стенд, окно обслуживания, откат</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28-29</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Обновления</t>
+          <t xml:space="preserve">Практика 8. Восстановление; Обновление</t>
         </is>
       </c>
       <c r="D28" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обновления закрывают уязвимости и добавляют функции, но могут сломать работу. Студент разберёт порядок установки, тестовый стенд, окно обслуживания и план отката.</t>
+          <t xml:space="preserve">Студент восстанавливает учебную базу из копии после смоделированного сбоя, затем устанавливает обновление на тестовый стенд и проверяет работу системы. Сдаёт протоколы восстановления и обновления.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">обновление, исправление, тестовый стенд, окно обслуживания, откат</t>
+          <t xml:space="preserve">восстановление, тестовый стенд, обновление, проверка после обновления, откат</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Безопасность</t>
+          <t xml:space="preserve">Лекция 16. Безопасность</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу: пароли, права, журналы, обновления, резервные копии. Сдаёт заполненный чек-лист с перечнем слабых мест и планом устранения.</t>
+          <t xml:space="preserve">Безопасность поддержки: разграничение доступа, защита каналов, журналирование действий и защита резервных копий. Студент разберёт типовые ошибки администрирования.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">парольная политика, права, уязвимость, журнал доступа, план устранения</t>
+          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование, защита копий</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Безопасность</t>
+          <t xml:space="preserve">Практика 9. Безопасность</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность поддержки: разграничение доступа, защита каналов, журналирование действий и защита резервных копий. Студент разберёт типовые ошибки администрирования.</t>
+          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу: пароли, права, журналы, обновления, резервные копии. Сдаёт заполненный чек-лист с перечнем слабых мест и планом устранения.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование, защита копий</t>
+          <t xml:space="preserve">парольная политика, права, уязвимость, журнал доступа, план устранения</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Доступы</t>
+          <t xml:space="preserve">Лекция 17. Доступы</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент оформляет и выполняет заявки на доступ: создаёт учётные записи, назначает роли, ограничивает права, блокирует уволенных. Сдаёт журнал доступов и матрицу ролей.</t>
+          <t xml:space="preserve">Управление доступами: учётные записи, роли, группы, права на объекты и регулярная проверка. Студент разберёт, как накапливаются лишние права и чем это опасно.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">учётная запись, роль, матрица прав, блокировка, заявка на доступ</t>
+          <t xml:space="preserve">учётная запись, роль, группа, проверка прав, отзыв доступа</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Доступы</t>
+          <t xml:space="preserve">Практика 10. Доступы</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление доступами: учётные записи, роли, группы, права на объекты и регулярная проверка. Студент разберёт, как накапливаются лишние права и чем это опасно.</t>
+          <t xml:space="preserve">Студент оформляет и выполняет заявки на доступ: создаёт учётные записи, назначает роли, ограничивает права, блокирует уволенных. Сдаёт журнал доступов и матрицу ролей.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">учётная запись, роль, группа, проверка прав, отзыв доступа</t>
+          <t xml:space="preserve">учётная запись, роль, матрица прав, блокировка, заявка на доступ</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. База знаний</t>
+          <t xml:space="preserve">Лекция 18. Документация</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пополняет базу знаний по учебной ИС: пишет статью по типовому обращению, прикладывает решение и проверяет её на коллеге. Сдаёт три статьи и результат проверки.</t>
+          <t xml:space="preserve">Документация поддержки: регламенты, инструкции, схемы инфраструктуры, журналы и отчёты. Студент разберёт, кто читает каждый документ и как поддерживать его в актуальном виде.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">статья, симптом, причина, решение, проверка статьи</t>
+          <t xml:space="preserve">регламент, инструкция, схема инфраструктуры, версия, актуализация</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Документация</t>
+          <t xml:space="preserve">Лекция 19. База знаний</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация поддержки: регламенты, инструкции, схемы инфраструктуры, журналы и отчёты. Студент разберёт, кто читает каждый документ и как поддерживать его в актуальном виде.</t>
+          <t xml:space="preserve">База знаний снижает нагрузку на поддержку и ускоряет решение. Студент разберёт структуру статей, поиск, проверку актуальности и связь статей с обращениями.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">регламент, инструкция, схема инфраструктуры, версия, актуализация</t>
+          <t xml:space="preserve">статья, категория, поиск, актуальность, типовое обращение</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Метрики</t>
+          <t xml:space="preserve">Практика 11. База знаний</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает метрики поддержки за период: число обращений, время реакции, время решения, доля выполненных SLA. Сдаёт сводную таблицу и графики с выводами.</t>
+          <t xml:space="preserve">Студент пополняет базу знаний по учебной ИС: пишет статью по типовому обращению, прикладывает решение и проверяет её на коллеге. Сдаёт три статьи и результат проверки.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">число обращений, время реакции, время решения, сводка, график</t>
+          <t xml:space="preserve">статья, симптом, причина, решение, проверка статьи</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. База знаний</t>
+          <t xml:space="preserve">Лекция 20. Коммуникации</t>
         </is>
       </c>
       <c r="D36" s="6">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">База знаний снижает нагрузку на поддержку и ускоряет решение. Студент разберёт структуру статей, поиск, проверку актуальности и связь статей с обращениями.</t>
+          <t xml:space="preserve">Поддержка это разговор с человеком в стрессе. Студент разберёт структуру обращения, уточняющие вопросы, информирование о ходе работ и работу с недовольным пользователем.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">статья, категория, поиск, актуальность, типовое обращение</t>
+          <t xml:space="preserve">уточняющий вопрос, структура обращения, информирование, конфликт, обратная связь</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 13. Отчёт</t>
+          <t xml:space="preserve">Лекция 21. Аутсорсинг</t>
         </is>
       </c>
       <c r="D37" s="6">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент готовит отчёт о работе поддержки за месяц: объём обращений, соблюдение SLA, повторные обращения, узкие места. Сдаёт отчёт с таблицами и предложениями.</t>
+          <t xml:space="preserve">Часть поддержки можно передать внешнему подрядчику. Студент разберёт, какие работы отдают на аутсорсинг, как описать услугу и что контролировать по договору.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">отчётный период, соблюдение SLA, повторное обращение, узкое место, предложение</t>
+          <t xml:space="preserve">аутсорсинг, подрядчик, договор, показатель услуги, контроль</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 20. Коммуникации</t>
+          <t xml:space="preserve">Лекция 22. Метрики</t>
         </is>
       </c>
       <c r="D38" s="6">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поддержка это разговор с человеком в стрессе. Студент разберёт структуру обращения, уточняющие вопросы, информирование о ходе работ и работу с недовольным пользователем.</t>
+          <t xml:space="preserve">Метрики поддержки показывают нагрузку, скорость и качество. Студент разберёт, какие показатели считать, как их не подделать и почему среднее время скрывает проблемы.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">уточняющий вопрос, структура обращения, информирование, конфликт, обратная связь</t>
+          <t xml:space="preserve">время реакции, время решения, повторное обращение, среднее и медиана, загрузка</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 14. Итоговый кейс</t>
+          <t xml:space="preserve">Практика 12. Метрики</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проходит полный цикл поддержки на учебном кейсе: приём обращения, диагностика, решение, запись в базу знаний, отчёт. Сдаёт пакет документов по кейсу.</t>
+          <t xml:space="preserve">Студент собирает метрики поддержки за период: число обращений, время реакции, время решения, доля выполненных SLA. Сдаёт сводную таблицу и графики с выводами.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">кейс, приём обращения, диагностика, закрытие, пакет документов</t>
+          <t xml:space="preserve">число обращений, время реакции, время решения, сводка, график</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 21. Аутсорсинг</t>
+          <t xml:space="preserve">Лекция 23. Отчётность</t>
         </is>
       </c>
       <c r="D40" s="6">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часть поддержки можно передать внешнему подрядчику. Студент разберёт, какие работы отдают на аутсорсинг, как описать услугу и что контролировать по договору.</t>
+          <t xml:space="preserve">Отчётность перед руководством и заказчиком: периодичность, состав показателей, выводы и предложения. Студент разберёт, как из журналов получается отчёт с решениями.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">аутсорсинг, подрядчик, договор, показатель услуги, контроль</t>
+          <t xml:space="preserve">структура отчёта, периодичность, показатель, вывод, предложение</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 22. Метрики</t>
+          <t xml:space="preserve">Практика 13. Отчёт</t>
         </is>
       </c>
       <c r="D41" s="6">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики поддержки показывают нагрузку, скорость и качество. Студент разберёт, какие показатели считать, как их не подделать и почему среднее время скрывает проблемы.</t>
+          <t xml:space="preserve">Студент готовит отчёт о работе поддержки за месяц: объём обращений, соблюдение SLA, повторные обращения, узкие места. Сдаёт отчёт с таблицами и предложениями.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">время реакции, время решения, повторное обращение, среднее и медиана, загрузка</t>
+          <t xml:space="preserve">отчётный период, соблюдение SLA, повторное обращение, узкое место, предложение</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 23. Отчётность</t>
+          <t xml:space="preserve">Лекция 24. Непрерывность</t>
         </is>
       </c>
       <c r="D42" s="6">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчётность перед руководством и заказчиком: периодичность, состав показателей, выводы и предложения. Студент разберёт, как из журналов получается отчёт с решениями.</t>
+          <t xml:space="preserve">Непрерывность бизнеса: что делать, если система недоступна. Студент разберёт план аварийного восстановления, резервные площадки и допустимое время простоя.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">структура отчёта, периодичность, показатель, вывод, предложение</t>
+          <t xml:space="preserve">непрерывность, аварийное восстановление, резервная площадка, время простоя, учебный запуск</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 24. Непрерывность</t>
+          <t xml:space="preserve">Практика 14. Итоговый кейс</t>
         </is>
       </c>
       <c r="D43" s="6">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Непрерывность бизнеса: что делать, если система недоступна. Студент разберёт план аварийного восстановления, резервные площадки и допустимое время простоя.</t>
+          <t xml:space="preserve">Студент проходит полный цикл поддержки на учебном кейсе: приём обращения, диагностика, решение, запись в базу знаний, отчёт. Сдаёт пакет документов по кейсу.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">непрерывность, аварийное восстановление, резервная площадка, время простоя, учебный запуск</t>
+          <t xml:space="preserve">кейс, приём обращения, диагностика, закрытие, пакет документов</t>
         </is>
       </c>
     </row>

--- a/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
+++ b/docs/4/is-support/Учебный_план_Инженерно-техническая_поддержка_сопровождения_ИС.xlsx
@@ -195,7 +195,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поддержка ИС охватывает пользователей, серверы, сеть, СУБД и данные. Студент разберёт, какие работы входят в поддержку, кто их выполняет и чем они отличаются от разработки.</t>
+          <t xml:space="preserve">Поддержка ИС охватывает пользователей, серверы, сеть, СУБД и данные. Вы разберёте, какие работы входят в поддержку, кто их выполняет и чем они отличаются от разработки.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITIL описывает поддержку как набор связанных процессов: инциденты, проблемы, изменения, запросы, релизы. Студент разберёт входы, выходы и владельцев каждого процесса.</t>
+          <t xml:space="preserve">ITIL описывает поддержку как набор связанных процессов: инциденты, проблемы, изменения, запросы, релизы. Вы разберёте входы, выходы и владельцев каждого процесса.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -255,7 +255,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA фиксирует обещание заказчику, SLO задаёт внутреннюю цель, SLI даёт измерение. Студент разберёт, как связаны три уровня и почему нельзя обещать больше, чем измеряешь.</t>
+          <t xml:space="preserve">SLA фиксирует обещание заказчику, SLO задаёт внутреннюю цель, SLI даёт измерение. Вы разберёте, как связаны три уровня и почему нельзя обещать больше, чем измеряешь.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Регламент поддержки; SLA</t>
+          <t xml:space="preserve">Практика 1. Карта услуг и уровни обслуживания</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,7 +285,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пишет регламент поддержки учебной ИС: каналы приёма, категории, сроки, эскалация. Затем составляет SLA с уровнями сервиса и условиями пересмотра. Сдаёт оба документа.</t>
+          <t xml:space="preserve">Регламент поддержки учебной ИС: каналы приёма, категории, сроки и эскалация, затем карта услуг с уровнями сервиса и условиями пересмотра. Результат: регламент и карта услуг.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -294,7 +294,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -315,7 +315,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инцидент это любое событие, которое снижает качество услуги. Студент разберёт приоритеты, сроки реакции, маршрут эскалации и порядок закрытия обращения.</t>
+          <t xml:space="preserve">Инцидент это любое событие, которое снижает качество услуги. Вы разберёте приоритеты, сроки реакции, маршрут эскалации и порядок закрытия обращения.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -345,7 +345,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проблема это неизвестная причина одного или нескольких инцидентов. Студент разберёт поиск корневой причины, временное обходное решение и постоянное исправление.</t>
+          <t xml:space="preserve">Проблема это неизвестная причина одного или нескольких инцидентов. Вы разберёте поиск корневой причины, временное обходное решение и постоянное исправление.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Инцидент; Проблема</t>
+          <t xml:space="preserve">Практика 2. Разбор серии сбоев и корневая причина</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,7 +375,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент обрабатывает серию инцидентов в учебной системе, находит общую причину и оформляет проблему. Сдаёт журнал инцидентов и карточку проблемы с планом устранения.</t>
+          <t xml:space="preserve">Обработка серии инцидентов в учебной системе, поиск общей причины и оформление проблемы. Результат: журнал инцидентов и карточка проблемы с планом устранения.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрос на обслуживание это штатная просьба пользователя: доступ, оборудование, консультация. Студент разберёт, чем запрос отличается от инцидента и как его выполнять по каталогу услуг.</t>
+          <t xml:space="preserve">Запрос на обслуживание это штатная просьба пользователя: доступ, оборудование, консультация. Вы разберёте, чем запрос отличается от инцидента и как его выполнять по каталогу услуг.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -435,7 +435,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг следит за доступностью, нагрузкой и ошибками системы. Студент разберёт виды датчиков, пороги срабатывания, оповещения и проблему ложных тревог.</t>
+          <t xml:space="preserve">Мониторинг следит за доступностью, нагрузкой и ошибками системы. Вы разберёте виды датчиков, пороги срабатывания, оповещения и проблему ложных тревог.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Запрос; Мониторинг</t>
+          <t xml:space="preserve">Практика 3. Каталог запросов и датчики доступности</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,7 +465,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент выполняет запросы пользователей по каталогу услуг и настраивает мониторинг учебного сервера: датчики, пороги, оповещения. Сдаёт журнал запросов и карту мониторинга.</t>
+          <t xml:space="preserve">Выполнение запросов пользователей по каталогу услуг и настройка мониторинга учебного сервера: датчики, пороги и оповещения. Результат: журнал запросов и карта мониторинга.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Журналы системы, приложения и безопасности фиксируют события с разной детализацией. Студент разберёт уровни записей, ротацию файлов и требования к хранению.</t>
+          <t xml:space="preserve">Журналы системы, приложения и безопасности фиксируют события с разной детализацией. Вы разберёте уровни записей, ротацию файлов и требования к хранению.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Журналы</t>
+          <t xml:space="preserve">Практика 4. Хронология сбоя по записям</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,7 +525,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент ищет причину сбоя по журналам учебного сервера и приложения: фильтрует записи по времени и уровню, сопоставляет события. Сдаёт выписку из журнала с разбором хронологии.</t>
+          <t xml:space="preserve">Поиск причины сбоя по журналам учебного сервера и приложения: фильтрация по времени и уровню, сопоставление событий. Результат: выписка из журнала с разбором хронологии.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика идёт от общего к частному: доступность узла, сеть, ресурсы, службы, приложение. Студент разберёт типовые симптомы и инструменты проверки на каждом шаге.</t>
+          <t xml:space="preserve">Диагностика идёт от общего к частному: доступность узла, сеть, ресурсы, службы, приложение. Вы разберёте типовые симптомы и инструменты проверки на каждом шаге.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Диагностика</t>
+          <t xml:space="preserve">Практика 5. Дерево проверок недоступного сервиса</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,7 +585,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент диагностирует сбой учебного сервера по шагам: проверяет питание и доступность, сеть, диск, службы, приложение. Сдаёт карту диагностики с найденной причиной.</t>
+          <t xml:space="preserve">Диагностика сбоя учебного сервера по шагам: доступность, сеть, диск, службы и приложение. Результат: карта диагностики с найденной причиной.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серверное железо и его ресурсы: процессор, память, диски, питание, охлаждение. Студент разберёт, как отказ каждого узла проявляется в работе ИС.</t>
+          <t xml:space="preserve">Серверное железо и его ресурсы: процессор, память, диски, питание, охлаждение. Вы разберёте, как отказ каждого узла проявляется в работе ИС.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сеть связывает пользователей с серверами ИС. Студент разберёт адресацию, маршрутизацию, порты и типовые причины потери связи с системой.</t>
+          <t xml:space="preserve">Сеть связывает пользователей с серверами ИС. Вы разберёте адресацию, маршрутизацию, порты и типовые причины потери связи с системой.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Сервер; Сеть</t>
+          <t xml:space="preserve">Практика 6. Проверка узла и маршрута</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,7 +675,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет учебный сервер и сеть до него: ресурсы, службы, адресацию, маршрут, порты. Сдаёт протокол проверки с найденными отклонениями и мерами устранения.</t>
+          <t xml:space="preserve">Проверка учебного сервера и сети до него: ресурсы, службы, адресация, маршрут и порты. Результат: протокол проверки с отклонениями и мерами устранения.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">СУБД отвечает за хранение и доступ к данным. Студент разберёт состояние экземпляра, блокировки, рост файлов и медленные запросы, которые чаще всего вызывают сбои.</t>
+          <t xml:space="preserve">СУБД отвечает за хранение и доступ к данным. Вы разберёте состояние экземпляра, блокировки, рост файлов и медленные запросы, которые чаще всего вызывают сбои.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервная копия защищает от потери данных, но только если её проверяют. Студент разберёт схемы копирования, глубину хранения и правило трёх копий.</t>
+          <t xml:space="preserve">Резервная копия защищает от потери данных, но только если её проверяют. Вы разберёте схемы копирования, глубину хранения и правило трёх копий.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. СУБД; Резервное копирование</t>
+          <t xml:space="preserve">Практика 7. Копия базы и проверка восстановления</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,7 +765,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет состояние учебной СУБД, затем делает полную и разностную копию базы, проверяет её целостность и восстанавливает на тестовый экземпляр. Сдаёт скрипты и протокол.</t>
+          <t xml:space="preserve">Проверка состояния учебной СУБД, полная и разностная копия базы, проверка целостности и восстановление на тестовый экземпляр. Результат: скрипты и протокол.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление возвращает систему к работе после сбоя. Студент разберёт точки восстановления, порядок действий, проверку целостности и фиксацию потерь данных.</t>
+          <t xml:space="preserve">Восстановление возвращает систему к работе после сбоя. Вы разберёте точки восстановления, порядок действий, проверку целостности и фиксацию потерь данных.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обновления закрывают уязвимости и добавляют функции, но могут сломать работу. Студент разберёт порядок установки, тестовый стенд, окно обслуживания и план отката.</t>
+          <t xml:space="preserve">Обновления закрывают уязвимости и добавляют функции, но могут сломать работу. Вы разберёте порядок установки, тестовый стенд, окно обслуживания и план отката.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Восстановление; Обновление</t>
+          <t xml:space="preserve">Практика 8. Откат после сбоя и установка обновления</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,7 +855,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент восстанавливает учебную базу из копии после смоделированного сбоя, затем устанавливает обновление на тестовый стенд и проверяет работу системы. Сдаёт протоколы восстановления и обновления.</t>
+          <t xml:space="preserve">Восстановление учебной базы из копии после смоделированного сбоя, установка обновления на тестовый стенд и проверка работы системы. Результат: протоколы восстановления и обновления.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность поддержки: разграничение доступа, защита каналов, журналирование действий и защита резервных копий. Студент разберёт типовые ошибки администрирования.</t>
+          <t xml:space="preserve">Безопасность поддержки: разграничение доступа, защита каналов, журналирование действий и защита резервных копий. Вы разберёте типовые ошибки администрирования.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Безопасность</t>
+          <t xml:space="preserve">Практика 9. Аудит паролей и прав</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,7 +915,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу: пароли, права, журналы, обновления, резервные копии. Сдаёт заполненный чек-лист с перечнем слабых мест и планом устранения.</t>
+          <t xml:space="preserve">Проверка учебной ИС по чек-листу: пароли, права, журналы, обновления и резервные копии. Результат: чек-лист с перечнем слабых мест и планом устранения.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление доступами: учётные записи, роли, группы, права на объекты и регулярная проверка. Студент разберёт, как накапливаются лишние права и чем это опасно.</t>
+          <t xml:space="preserve">Управление доступами: учётные записи, роли, группы, права на объекты и регулярная проверка. Вы разберёте, как накапливаются лишние права и чем это опасно.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Доступы</t>
+          <t xml:space="preserve">Практика 10. Заявки на доступ и матрица ролей</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,7 +975,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент оформляет и выполняет заявки на доступ: создаёт учётные записи, назначает роли, ограничивает права, блокирует уволенных. Сдаёт журнал доступов и матрицу ролей.</t>
+          <t xml:space="preserve">Оформление и выполнение заявок на доступ: создание учётных записей, назначение ролей, ограничение прав и блокировка уволенных. Результат: журнал доступов и матрица ролей.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация поддержки: регламенты, инструкции, схемы инфраструктуры, журналы и отчёты. Студент разберёт, кто читает каждый документ и как поддерживать его в актуальном виде.</t>
+          <t xml:space="preserve">Документация поддержки: регламенты, инструкции, схемы инфраструктуры, журналы и отчёты. Вы разберёте, кто читает каждый документ и как поддерживать его в актуальном виде.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">База знаний снижает нагрузку на поддержку и ускоряет решение. Студент разберёт структуру статей, поиск, проверку актуальности и связь статей с обращениями.</t>
+          <t xml:space="preserve">База знаний снижает нагрузку на поддержку и ускоряет решение. Вы разберёте структуру статей, поиск, проверку актуальности и связь статей с обращениями.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. База знаний</t>
+          <t xml:space="preserve">Практика 11. Статья для типового обращения</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пополняет базу знаний по учебной ИС: пишет статью по типовому обращению, прикладывает решение и проверяет её на коллеге. Сдаёт три статьи и результат проверки.</t>
+          <t xml:space="preserve">Пополнение базы знаний по учебной ИС: статья по типовому обращению, решение и проверка на коллеге. Результат: три статьи и результат проверки.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поддержка это разговор с человеком в стрессе. Студент разберёт структуру обращения, уточняющие вопросы, информирование о ходе работ и работу с недовольным пользователем.</t>
+          <t xml:space="preserve">Поддержка это разговор с человеком в стрессе. Вы разберёте структуру обращения, уточняющие вопросы, информирование о ходе работ и работу с недовольным пользователем.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часть поддержки можно передать внешнему подрядчику. Студент разберёт, какие работы отдают на аутсорсинг, как описать услугу и что контролировать по договору.</t>
+          <t xml:space="preserve">Часть поддержки можно передать внешнему подрядчику. Вы разберёте, какие работы отдают на аутсорсинг, как описать услугу и что контролировать по договору.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики поддержки показывают нагрузку, скорость и качество. Студент разберёт, какие показатели считать, как их не подделать и почему среднее время скрывает проблемы.</t>
+          <t xml:space="preserve">Метрики поддержки показывают нагрузку, скорость и качество. Вы разберёте, какие показатели считать, как их не подделать и почему среднее время скрывает проблемы.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Метрики</t>
+          <t xml:space="preserve">Практика 12. Сводка обращений и соблюдение сроков</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает метрики поддержки за период: число обращений, время реакции, время решения, доля выполненных SLA. Сдаёт сводную таблицу и графики с выводами.</t>
+          <t xml:space="preserve">Сбор метрик поддержки за период: число обращений, время реакции и решения, доля выполненных SLA. Результат: сводная таблица и графики с выводами.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчётность перед руководством и заказчиком: периодичность, состав показателей, выводы и предложения. Студент разберёт, как из журналов получается отчёт с решениями.</t>
+          <t xml:space="preserve">Отчётность перед руководством и заказчиком: периодичность, состав показателей, выводы и предложения. Вы разберёте, как из журналов получается отчёт с решениями.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 13. Отчёт</t>
+          <t xml:space="preserve">Практика 13. Месячная сводка для заказчика</t>
         </is>
       </c>
       <c r="D41" s="6">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент готовит отчёт о работе поддержки за месяц: объём обращений, соблюдение SLA, повторные обращения, узкие места. Сдаёт отчёт с таблицами и предложениями.</t>
+          <t xml:space="preserve">Отчёт о работе поддержки за месяц: объём обращений, соблюдение SLA, повторные обращения и узкие места. Результат: отчёт с таблицами и предложениями.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Непрерывность бизнеса: что делать, если система недоступна. Студент разберёт план аварийного восстановления, резервные площадки и допустимое время простоя.</t>
+          <t xml:space="preserve">Непрерывность бизнеса: что делать, если система недоступна. Вы разберёте план аварийного восстановления, резервные площадки и допустимое время простоя.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" ht="45" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 14. Итоговый кейс</t>
+          <t xml:space="preserve">Практика 14. Разбор крупного сбоя</t>
         </is>
       </c>
       <c r="D43" s="6">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проходит полный цикл поддержки на учебном кейсе: приём обращения, диагностика, решение, запись в базу знаний, отчёт. Сдаёт пакет документов по кейсу.</t>
+          <t xml:space="preserve">Полный цикл поддержки на учебном кейсе: приём обращения, диагностика, решение, запись в базу знаний и отчёт. Результат: пакет документов по кейсу.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
